--- a/data/outputs/table_status_analysis.xlsx
+++ b/data/outputs/table_status_analysis.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/075977bab84aedd4/Documents/AI_restaurant/data/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_6882BDEF0196C6B9866289BB862D3E0C84C58CE3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B76BDD97-63CD-4037-9D38-D9A4A95274D2}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_71F8A113E92BE63D8380181CE81EB772FF1DDBF7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40158C7-70E1-4DEB-A606-8F8F97030C83}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15285" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
     <sheet name="Inefficient Tables" sheetId="2" r:id="rId2"/>
-    <sheet name="Table Cycle Duration" sheetId="3" r:id="rId3"/>
-    <sheet name="Average Analysis" sheetId="4" r:id="rId4"/>
-    <sheet name="Histogram" sheetId="5" r:id="rId5"/>
-    <sheet name="Status Analysis" sheetId="6" r:id="rId6"/>
+    <sheet name="Average Analysis" sheetId="3" r:id="rId3"/>
+    <sheet name="Histogram" sheetId="4" r:id="rId4"/>
+    <sheet name="Status Analysis" sheetId="5" r:id="rId5"/>
+    <sheet name="cycle_duration_histograms" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="61">
   <si>
     <t>available</t>
   </si>
@@ -69,27 +69,60 @@
     <t>00:10:00</t>
   </si>
   <si>
+    <t>2024-11-15 10:35:30</t>
+  </si>
+  <si>
+    <t>00:25:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:45:30</t>
+  </si>
+  <si>
+    <t>00:50:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:10:30</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 12:00:30</t>
+  </si>
+  <si>
+    <t>Afternoon</t>
+  </si>
+  <si>
     <t>2024-11-15 08:40:00</t>
   </si>
   <si>
-    <t>00:25:00</t>
-  </si>
-  <si>
     <t>2024-11-15 08:50:00</t>
   </si>
   <si>
-    <t>00:50:00</t>
-  </si>
-  <si>
     <t>2024-11-15 09:15:00</t>
   </si>
   <si>
-    <t>00:15:00</t>
-  </si>
-  <si>
     <t>2024-11-15 10:05:00</t>
   </si>
   <si>
+    <t>00:08:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:20:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:28:00</t>
+  </si>
+  <si>
+    <t>00:40:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:48:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:28:00</t>
+  </si>
+  <si>
     <t>00:12:00</t>
   </si>
   <si>
@@ -108,7 +141,16 @@
     <t>2024-11-15 10:42:00</t>
   </si>
   <si>
-    <t>00:08:00</t>
+    <t>2024-11-15 11:07:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:17:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:47:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 12:37:00</t>
   </si>
   <si>
     <t>2024-11-15 10:00:00</t>
@@ -129,91 +171,16 @@
     <t>2024-11-15 11:38:00</t>
   </si>
   <si>
-    <t>2024-11-15 10:30:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:50:00</t>
-  </si>
-  <si>
-    <t>01:20:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:20:00</t>
-  </si>
-  <si>
-    <t>00:40:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 12:40:00</t>
-  </si>
-  <si>
-    <t>Afternoon</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:30:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:45:00</t>
-  </si>
-  <si>
-    <t>00:45:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:10:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:55:00</t>
-  </si>
-  <si>
-    <t>00:05:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 08:00:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 08:05:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 08:25:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:05:00</t>
-  </si>
-  <si>
-    <t>00:07:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:00:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:07:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:22:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:57:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 07:30:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 07:50:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:50:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:27:00</t>
-  </si>
-  <si>
-    <t>01:30:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:47:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:17:00</t>
+    <t>2024-11-15 12:08:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 12:23:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 12:48:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 13:48:00</t>
   </si>
   <si>
     <t>Table ID</t>
@@ -228,37 +195,13 @@
     <t>Inefficient</t>
   </si>
   <si>
-    <t>02:50:00</t>
-  </si>
-  <si>
-    <t>02:00:00</t>
-  </si>
-  <si>
-    <t>02:47:00</t>
-  </si>
-  <si>
-    <t>Cycle Duration</t>
-  </si>
-  <si>
-    <t>02:05:30</t>
-  </si>
-  <si>
-    <t>01:40:00</t>
-  </si>
-  <si>
-    <t>02:07:00</t>
-  </si>
-  <si>
-    <t>02:08:00</t>
-  </si>
-  <si>
-    <t>01:15:00</t>
-  </si>
-  <si>
-    <t>01:17:00</t>
-  </si>
-  <si>
-    <t>02:45:00</t>
+    <t>03:45:30</t>
+  </si>
+  <si>
+    <t>03:57:00</t>
+  </si>
+  <si>
+    <t>04:18:00</t>
   </si>
   <si>
     <t>Max Duration</t>
@@ -334,7 +277,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -367,7 +310,7 @@
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -405,7 +348,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -432,12 +375,54 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9525000" cy="5715000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4286250" y="0"/>
+          <a:ext cx="9525000" cy="5715000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9525000" cy="5715000"/>
+    <xdr:ext cx="11430000" cy="7620000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
@@ -456,6 +441,43 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>133598</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="11430000" cy="7620000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11767705" y="0"/>
+          <a:ext cx="11430000" cy="7620000"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -751,13 +773,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1">
@@ -829,7 +846,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -846,7 +863,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -863,7 +880,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -880,7 +897,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -892,18 +909,18 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -914,13 +931,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -931,16 +948,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
@@ -948,16 +965,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
@@ -965,16 +982,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
       </c>
       <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
         <v>27</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
@@ -982,16 +999,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
@@ -999,16 +1016,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
@@ -1016,16 +1033,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
@@ -1033,16 +1050,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
@@ -1050,16 +1067,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
@@ -1067,16 +1084,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="s">
         <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
@@ -1084,33 +1101,33 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
@@ -1118,16 +1135,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
@@ -1135,16 +1152,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
@@ -1152,33 +1169,33 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
@@ -1186,16 +1203,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
@@ -1203,16 +1220,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
@@ -1220,16 +1237,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
@@ -1237,206 +1254,70 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>9</v>
-      </c>
-      <c r="B33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>9</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>10</v>
-      </c>
-      <c r="B37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C37" t="s">
         <v>21</v>
-      </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>10</v>
-      </c>
-      <c r="B38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>10</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>10</v>
-      </c>
-      <c r="B40" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1448,53 +1329,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1504,103 +1381,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1616,9 +1401,70 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1626,65 +1472,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/outputs/table_status_analysis.xlsx
+++ b/data/outputs/table_status_analysis.xlsx
@@ -8,24 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/075977bab84aedd4/Documents/AI_restaurant/data/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_71F8A113E92BE63D8380181CE81EB772FF1DDBF7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40158C7-70E1-4DEB-A606-8F8F97030C83}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_ACD5E0C99D8D71638257BA1765D20BAA4E084B03" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7975CA16-82E6-4747-AB7B-30E9D7DD7D61}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="15285" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Inefficient Tables" sheetId="2" r:id="rId2"/>
-    <sheet name="Average Analysis" sheetId="3" r:id="rId3"/>
-    <sheet name="Histogram" sheetId="4" r:id="rId4"/>
-    <sheet name="Status Analysis" sheetId="5" r:id="rId5"/>
-    <sheet name="cycle_duration_histograms" sheetId="6" r:id="rId6"/>
+    <sheet name="Average Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="Histogram" sheetId="3" r:id="rId3"/>
+    <sheet name="Status Analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="cycle_duration_histograms" sheetId="5" r:id="rId5"/>
+    <sheet name="Table Performance" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Table Performance'!$A$1:$L$11</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="89">
   <si>
     <t>available</t>
   </si>
@@ -69,145 +72,229 @@
     <t>00:10:00</t>
   </si>
   <si>
-    <t>2024-11-15 10:35:30</t>
+    <t>2024-11-15 08:40:00</t>
   </si>
   <si>
     <t>00:25:00</t>
   </si>
   <si>
-    <t>2024-11-15 10:45:30</t>
+    <t>2024-11-15 08:50:00</t>
   </si>
   <si>
     <t>00:50:00</t>
   </si>
   <si>
-    <t>2024-11-15 11:10:30</t>
+    <t>2024-11-15 09:15:00</t>
   </si>
   <si>
     <t>00:15:00</t>
   </si>
   <si>
-    <t>2024-11-15 12:00:30</t>
+    <t>2024-11-15 10:05:00</t>
+  </si>
+  <si>
+    <t>00:12:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:00:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:12:00</t>
+  </si>
+  <si>
+    <t>01:10:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:32:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:42:00</t>
+  </si>
+  <si>
+    <t>00:08:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:00:00</t>
+  </si>
+  <si>
+    <t>00:35:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:08:00</t>
+  </si>
+  <si>
+    <t>00:55:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:43:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:38:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:30:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:50:00</t>
+  </si>
+  <si>
+    <t>01:20:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:20:00</t>
+  </si>
+  <si>
+    <t>00:40:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 12:40:00</t>
   </si>
   <si>
     <t>Afternoon</t>
   </si>
   <si>
-    <t>2024-11-15 08:40:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 08:50:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:15:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:05:00</t>
-  </si>
-  <si>
-    <t>00:08:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:20:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:28:00</t>
-  </si>
-  <si>
-    <t>00:40:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:48:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:28:00</t>
-  </si>
-  <si>
-    <t>00:12:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:00:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:12:00</t>
-  </si>
-  <si>
-    <t>01:10:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 09:32:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:42:00</t>
+    <t>2024-11-15 09:30:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:45:00</t>
+  </si>
+  <si>
+    <t>00:45:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:10:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 10:55:00</t>
+  </si>
+  <si>
+    <t>00:05:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 08:00:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 08:05:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 08:25:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:05:00</t>
+  </si>
+  <si>
+    <t>00:07:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:00:00</t>
   </si>
   <si>
     <t>2024-11-15 11:07:00</t>
   </si>
   <si>
+    <t>2024-11-15 11:22:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 11:57:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 07:30:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 07:50:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:50:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:27:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>2024-11-15 09:47:00</t>
+  </si>
+  <si>
     <t>2024-11-15 11:17:00</t>
   </si>
   <si>
-    <t>2024-11-15 11:47:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 12:37:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:00:00</t>
-  </si>
-  <si>
-    <t>00:35:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:08:00</t>
-  </si>
-  <si>
-    <t>00:55:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 10:43:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 11:38:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 12:08:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 12:23:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 12:48:00</t>
-  </si>
-  <si>
-    <t>2024-11-15 13:48:00</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Max Duration</t>
+  </si>
+  <si>
+    <t>Min Duration</t>
   </si>
   <si>
     <t>Table ID</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Total Duration</t>
-  </si>
-  <si>
-    <t>Inefficient</t>
-  </si>
-  <si>
-    <t>03:45:30</t>
-  </si>
-  <si>
-    <t>03:57:00</t>
-  </si>
-  <si>
-    <t>04:18:00</t>
-  </si>
-  <si>
-    <t>Max Duration</t>
-  </si>
-  <si>
-    <t>Min Duration</t>
+    <t>Total Time</t>
+  </si>
+  <si>
+    <t>Total Cycles</t>
+  </si>
+  <si>
+    <t>Time Eating</t>
+  </si>
+  <si>
+    <t>Time Ready to Order</t>
+  </si>
+  <si>
+    <t>Time Need to Clean</t>
+  </si>
+  <si>
+    <t>Time Available</t>
+  </si>
+  <si>
+    <t>Idle Time Ratio</t>
+  </si>
+  <si>
+    <t>Cleaning Ratio</t>
+  </si>
+  <si>
+    <t>Cycles per Hour</t>
+  </si>
+  <si>
+    <t>Utilization Rate</t>
+  </si>
+  <si>
+    <t>Performance Score</t>
+  </si>
+  <si>
+    <t>02:05:30</t>
+  </si>
+  <si>
+    <t>00:00:01</t>
+  </si>
+  <si>
+    <t>01:40:00</t>
+  </si>
+  <si>
+    <t>02:07:00</t>
+  </si>
+  <si>
+    <t>02:08:00</t>
+  </si>
+  <si>
+    <t>02:50:00</t>
+  </si>
+  <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
+    <t>01:15:00</t>
+  </si>
+  <si>
+    <t>01:17:00</t>
+  </si>
+  <si>
+    <t>02:45:00</t>
+  </si>
+  <si>
+    <t>02:47:00</t>
   </si>
 </sst>
 </file>
@@ -277,7 +364,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -310,7 +397,7 @@
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -348,7 +435,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -375,8 +462,8 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -386,7 +473,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -399,10 +486,6 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4286250" y="0"/>
-          <a:ext cx="9525000" cy="5715000"/>
-        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -428,7 +511,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -450,9 +533,9 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>133598</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="11430000" cy="7620000"/>
@@ -461,7 +544,7 @@
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -474,10 +557,6 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11767705" y="0"/>
-          <a:ext cx="11430000" cy="7620000"/>
-        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -773,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -846,7 +925,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -863,7 +942,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -880,7 +959,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -897,7 +976,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -909,18 +988,18 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -931,13 +1010,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -948,16 +1027,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
@@ -965,16 +1044,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
@@ -982,16 +1061,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
@@ -999,16 +1078,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
@@ -1016,16 +1095,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
@@ -1033,16 +1112,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
@@ -1050,16 +1129,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
@@ -1067,16 +1146,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
@@ -1084,16 +1163,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
         <v>3</v>
@@ -1101,33 +1180,33 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
@@ -1135,16 +1214,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
@@ -1152,16 +1231,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
@@ -1169,33 +1248,33 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
@@ -1203,16 +1282,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
@@ -1220,16 +1299,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
@@ -1237,16 +1316,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
@@ -1254,70 +1333,206 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
         <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1327,55 +1542,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1391,6 +1562,72 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1399,83 +1636,434 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C5"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="12" max="12" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0.1235059760956175</v>
+      </c>
+      <c r="I2">
+        <v>0.15936254980079681</v>
+      </c>
+      <c r="J2">
+        <v>0.4780876494023904</v>
+      </c>
+      <c r="K2">
+        <v>0.71713147410358569</v>
+      </c>
+      <c r="L2">
+        <v>9.9256308100929613E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3">
+        <v>0.1</v>
+      </c>
+      <c r="I3">
+        <v>0.15</v>
+      </c>
+      <c r="J3">
+        <v>0.6</v>
+      </c>
+      <c r="K3">
+        <v>0.75</v>
+      </c>
+      <c r="L3">
+        <v>0.1100666666666666</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>9.4488188976377951E-2</v>
+      </c>
+      <c r="I4">
+        <v>0.19685039370078741</v>
+      </c>
+      <c r="J4">
+        <v>0.47244094488188981</v>
+      </c>
+      <c r="K4">
+        <v>0.70866141732283461</v>
+      </c>
+      <c r="L4">
+        <v>0.1165879265091863</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="I5">
+        <v>0.234375</v>
+      </c>
+      <c r="J5">
+        <v>0.46875</v>
+      </c>
+      <c r="K5">
+        <v>0.703125</v>
+      </c>
+      <c r="L5">
+        <v>7.5833333333333336E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="I6">
+        <v>0.23529411764705879</v>
+      </c>
+      <c r="J6">
+        <v>0.3529411764705882</v>
+      </c>
+      <c r="K6">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="L6">
+        <v>8.2392156862745106E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>0.125</v>
+      </c>
+      <c r="I7">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="J7">
+        <v>0.5</v>
+      </c>
+      <c r="K7">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L7">
+        <v>4.1722222222222202E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="I8">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="J8">
+        <v>0.8</v>
+      </c>
+      <c r="K8">
+        <v>0.8</v>
+      </c>
+      <c r="L8">
+        <v>0.12675555555555559</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="I9">
+        <v>0.25974025974025972</v>
+      </c>
+      <c r="J9">
+        <v>0.77922077922077915</v>
+      </c>
+      <c r="K9">
+        <v>0.64935064935064934</v>
+      </c>
+      <c r="L9">
+        <v>7.5411255411255401E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>0.1212121212121212</v>
+      </c>
+      <c r="I10">
+        <v>0.15151515151515149</v>
+      </c>
+      <c r="J10">
+        <v>0.36363636363636359</v>
+      </c>
+      <c r="K10">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="L10">
+        <v>8.4888888888888875E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>43</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11">
+        <v>7.1856287425149698E-2</v>
+      </c>
+      <c r="I11">
+        <v>0.26946107784431139</v>
+      </c>
+      <c r="J11">
+        <v>0.3592814371257485</v>
+      </c>
+      <c r="K11">
+        <v>0.6586826347305389</v>
+      </c>
+      <c r="L11">
+        <v>0.1006387225548902</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L11" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/outputs/table_status_analysis.xlsx
+++ b/data/outputs/table_status_analysis.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Max People per Hour" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Table Performance'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Table Performance'!$A$1:$L$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -622,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,17 +636,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -661,17 +661,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -686,17 +686,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -711,17 +711,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -761,17 +761,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -811,67 +811,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-11-19 17:09:45</t>
+          <t>2024-11-19 21:30:59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Afternoon</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2024-11-19 17:09:45</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00:00:02</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Afternoon</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>available</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2024-11-19 17:09:45</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>00:00:02</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -942,12 +892,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
     </row>
@@ -977,7 +927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,7 +998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1073,7 +1023,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -1098,7 +1048,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1123,7 +1073,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1148,7 +1098,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1173,7 +1123,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1198,7 +1148,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1223,7 +1173,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1248,7 +1198,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,7 +1223,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1298,7 +1248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1323,7 +1273,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1348,7 +1298,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1373,7 +1323,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1398,7 +1348,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1423,7 +1373,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>00:00:02</t>
+          <t>00:00:24</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1442,108 +1392,8 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>00:00:02</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>00:00:02</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>00:00:02</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00:00:00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>00:00:02</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1586,11 +1436,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
